--- a/data/public-data2.xlsx
+++ b/data/public-data2.xlsx
@@ -6,13 +6,16 @@
   </bookViews>
   <sheets>
     <sheet name="第十九屆北區聯合新生盃辯論比賽" sheetId="1" r:id="rId4"/>
-    <sheet name="第一屆青雲盃全國高中職辯論錦標賽" sheetId="2" r:id="rId5"/>
+    <sheet name="第二十一屆齊揚盃" sheetId="2" r:id="rId5"/>
+    <sheet name="第一屆夢箋盃" sheetId="3" r:id="rId6"/>
+    <sheet name="第十屆雲啟盃辯論比賽" sheetId="4" r:id="rId7"/>
+    <sheet name="第一屆青雲盃全國高中職辯論錦標賽" sheetId="5" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="149">
   <si>
     <t>public-data2</t>
   </si>
@@ -221,6 +224,176 @@
     <t>Player</t>
   </si>
   <si>
+    <t>第二十一屆齊揚盃</t>
+  </si>
+  <si>
+    <t>憂鬱文學的興起對現代年輕族群是利大於弊/弊大於利</t>
+  </si>
+  <si>
+    <t>北一女中</t>
+  </si>
+  <si>
+    <t>師大附中</t>
+  </si>
+  <si>
+    <t>小港高中</t>
+  </si>
+  <si>
+    <t>臺中一中</t>
+  </si>
+  <si>
+    <t>臺南一中</t>
+  </si>
+  <si>
+    <t>中山高中</t>
+  </si>
+  <si>
+    <t>臺南二中</t>
+  </si>
+  <si>
+    <t>東港高中</t>
+  </si>
+  <si>
+    <t>建國中學</t>
+  </si>
+  <si>
+    <t>明道中學</t>
+  </si>
+  <si>
+    <t>興大附中</t>
+  </si>
+  <si>
+    <t>中山女高</t>
+  </si>
+  <si>
+    <t>平鎮高中</t>
+  </si>
+  <si>
+    <t>新竹高商</t>
+  </si>
+  <si>
+    <t>家齊高中</t>
+  </si>
+  <si>
+    <t>市立東山</t>
+  </si>
+  <si>
+    <t>竹科實中</t>
+  </si>
+  <si>
+    <t>中信國際</t>
+  </si>
+  <si>
+    <t>曉明女中</t>
+  </si>
+  <si>
+    <t>冠亞賽；原公告註記：因有一張評分單平分，故以論點分判定</t>
+  </si>
+  <si>
+    <t>林軒嘉</t>
+  </si>
+  <si>
+    <t>陳筳皓</t>
+  </si>
+  <si>
+    <t>蘇博原</t>
+  </si>
+  <si>
+    <t>蔡秉譯</t>
+  </si>
+  <si>
+    <t>第一屆夢箋盃</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我國成年人性別變更登記應採自我決定模式 (self-determination model)
+</t>
+  </si>
+  <si>
+    <t>附加定義：自我決定模式係指不需針對性別認同提供醫療或其他非醫療的證明，亦毋庸透過法院裁決，僅須於行政程序經自我宣稱
+（self-declaration）變更性別登記。</t>
+  </si>
+  <si>
+    <t>2025-04-12</t>
+  </si>
+  <si>
+    <t>明倫高中</t>
+  </si>
+  <si>
+    <t>中壢高商</t>
+  </si>
+  <si>
+    <t>立人高中</t>
+  </si>
+  <si>
+    <t>衛道中學</t>
+  </si>
+  <si>
+    <t>永豐高中</t>
+  </si>
+  <si>
+    <t>2025-04-13</t>
+  </si>
+  <si>
+    <t>李鎧麟</t>
+  </si>
+  <si>
+    <t>方凱佾</t>
+  </si>
+  <si>
+    <t>陳佳皇</t>
+  </si>
+  <si>
+    <t>孫興宸</t>
+  </si>
+  <si>
+    <t>第十屆雲啟盃辯論比賽</t>
+  </si>
+  <si>
+    <t>我國應設立投票權行使之前提性公民素養標準</t>
+  </si>
+  <si>
+    <t>斗六高中</t>
+  </si>
+  <si>
+    <t>虎尾高中（二）</t>
+  </si>
+  <si>
+    <t>馬公高中（一）</t>
+  </si>
+  <si>
+    <t>虎尾高中（一）</t>
+  </si>
+  <si>
+    <t>新竹高中（一）</t>
+  </si>
+  <si>
+    <t>馬公高中（二）</t>
+  </si>
+  <si>
+    <t>員林高中</t>
+  </si>
+  <si>
+    <t>聖功女中</t>
+  </si>
+  <si>
+    <t>虎尾高中（三）</t>
+  </si>
+  <si>
+    <t>新竹高中（二）</t>
+  </si>
+  <si>
+    <t>殿軍</t>
+  </si>
+  <si>
+    <t>徐愷宏</t>
+  </si>
+  <si>
+    <t>陳品捷</t>
+  </si>
+  <si>
+    <t>林子芹</t>
+  </si>
+  <si>
     <t>第一屆青雲盃全國高中職辯論錦標賽</t>
   </si>
   <si>
@@ -230,9 +403,6 @@
     <t>2024-05-25</t>
   </si>
   <si>
-    <t>中山女高</t>
-  </si>
-  <si>
     <t>高市中正</t>
   </si>
   <si>
@@ -260,9 +430,6 @@
     <t>；高市中正B因選手未到，故以棄賽論</t>
   </si>
   <si>
-    <t>中山高中</t>
-  </si>
-  <si>
     <t>小港高中A</t>
   </si>
   <si>
@@ -282,9 +449,6 @@
   </si>
   <si>
     <t>；未公告比分，依最終名次判定勝方</t>
-  </si>
-  <si>
-    <t>殿軍</t>
   </si>
   <si>
     <t>林華慈</t>
@@ -306,10 +470,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="4">
     <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="59" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="60" formatCode="yyyy-m-d"/>
+    <numFmt numFmtId="61" formatCode="yyyy/m/d"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -347,6 +514,16 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica"/>
     </font>
   </fonts>
   <fills count="7">
@@ -387,7 +564,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -725,13 +902,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="12"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -856,6 +1044,48 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="0" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="29" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="59" fontId="0" fillId="2" borderId="26" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="60" fontId="0" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="61" fontId="0" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -1170,10 +1400,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1721,10 +1951,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -4070,7 +4300,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.85" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.17188" style="42" customWidth="1"/>
@@ -4088,9 +4318,3828 @@
     <col min="16" max="16384" width="8.35156" style="42" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" ht="27.6" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" ht="21.7" customHeight="1">
+      <c r="A2" t="s" s="5">
+        <v>69</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" ht="13.1" customHeight="1">
+      <c r="A3" t="s" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s" s="9">
+        <v>69</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" t="s" s="9">
+        <v>3</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" ht="20.25" customHeight="1">
+      <c r="A4" t="s" s="12">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="13">
+        <v>70</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" t="s" s="16">
+        <v>6</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="19"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" t="s" s="16">
+        <v>7</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="19"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" t="s" s="20">
+        <v>8</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="23"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" t="s" s="29">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s" s="30">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s" s="30">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s" s="30">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s" s="30">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s" s="30">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s" s="30">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s" s="30">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s" s="30">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s" s="30">
+        <v>19</v>
+      </c>
+      <c r="L8" t="s" s="30">
+        <v>20</v>
+      </c>
+      <c r="M8" t="s" s="30">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s" s="30">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s" s="43">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C9" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D9" s="45">
+        <v>1</v>
+      </c>
+      <c r="E9" s="45">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s" s="34">
+        <v>71</v>
+      </c>
+      <c r="G9" t="s" s="34">
+        <v>72</v>
+      </c>
+      <c r="H9" s="45">
+        <v>1</v>
+      </c>
+      <c r="I9" s="45">
+        <v>2</v>
+      </c>
+      <c r="J9" t="s" s="34">
+        <v>72</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="19"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C10" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D10" s="45">
+        <v>1</v>
+      </c>
+      <c r="E10" s="45">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s" s="34">
+        <v>52</v>
+      </c>
+      <c r="G10" t="s" s="34">
+        <v>73</v>
+      </c>
+      <c r="H10" s="45">
+        <v>3</v>
+      </c>
+      <c r="I10" s="45">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s" s="34">
+        <v>52</v>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="19"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C11" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D11" s="45">
+        <v>1</v>
+      </c>
+      <c r="E11" s="45">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s" s="34">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s" s="34">
+        <v>42</v>
+      </c>
+      <c r="H11" s="45">
+        <v>1</v>
+      </c>
+      <c r="I11" s="45">
+        <v>2</v>
+      </c>
+      <c r="J11" t="s" s="34">
+        <v>42</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="19"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C12" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D12" s="45">
+        <v>1</v>
+      </c>
+      <c r="E12" s="45">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s" s="34">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="H12" s="45">
+        <v>2</v>
+      </c>
+      <c r="I12" s="45">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s" s="34">
+        <v>74</v>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="19"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C13" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D13" s="45">
+        <v>1</v>
+      </c>
+      <c r="E13" s="45">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s" s="34">
+        <v>76</v>
+      </c>
+      <c r="G13" t="s" s="34">
+        <v>77</v>
+      </c>
+      <c r="H13" s="45">
+        <v>0</v>
+      </c>
+      <c r="I13" s="45">
+        <v>3</v>
+      </c>
+      <c r="J13" t="s" s="34">
+        <v>77</v>
+      </c>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="19"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C14" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D14" s="45">
+        <v>1</v>
+      </c>
+      <c r="E14" s="45">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s" s="34">
+        <v>78</v>
+      </c>
+      <c r="G14" t="s" s="34">
+        <v>79</v>
+      </c>
+      <c r="H14" s="45">
+        <v>1</v>
+      </c>
+      <c r="I14" s="45">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s" s="34">
+        <v>79</v>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="19"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C15" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D15" s="45">
+        <v>1</v>
+      </c>
+      <c r="E15" s="45">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s" s="34">
+        <v>81</v>
+      </c>
+      <c r="H15" s="45">
+        <v>3</v>
+      </c>
+      <c r="I15" s="45">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="19"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C16" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D16" s="45">
+        <v>1</v>
+      </c>
+      <c r="E16" s="45">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s" s="34">
+        <v>55</v>
+      </c>
+      <c r="G16" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="H16" s="45">
+        <v>1</v>
+      </c>
+      <c r="I16" s="45">
+        <v>2</v>
+      </c>
+      <c r="J16" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C17" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D17" s="45">
+        <v>2</v>
+      </c>
+      <c r="E17" s="45">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s" s="34">
+        <v>83</v>
+      </c>
+      <c r="G17" t="s" s="34">
+        <v>71</v>
+      </c>
+      <c r="H17" s="45">
+        <v>1</v>
+      </c>
+      <c r="I17" s="45">
+        <v>2</v>
+      </c>
+      <c r="J17" t="s" s="34">
+        <v>71</v>
+      </c>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="19"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C18" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D18" s="45">
+        <v>2</v>
+      </c>
+      <c r="E18" s="45">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="G18" t="s" s="34">
+        <v>52</v>
+      </c>
+      <c r="H18" s="45">
+        <v>3</v>
+      </c>
+      <c r="I18" s="45">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="19"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C19" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D19" s="45">
+        <v>2</v>
+      </c>
+      <c r="E19" s="45">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s" s="34">
+        <v>84</v>
+      </c>
+      <c r="G19" t="s" s="34">
+        <v>36</v>
+      </c>
+      <c r="H19" s="45">
+        <v>1</v>
+      </c>
+      <c r="I19" s="45">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s" s="34">
+        <v>36</v>
+      </c>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="19"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C20" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D20" s="45">
+        <v>2</v>
+      </c>
+      <c r="E20" s="45">
+        <v>4</v>
+      </c>
+      <c r="F20" t="s" s="34">
+        <v>85</v>
+      </c>
+      <c r="G20" t="s" s="34">
+        <v>74</v>
+      </c>
+      <c r="H20" s="45">
+        <v>2</v>
+      </c>
+      <c r="I20" s="45">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s" s="34">
+        <v>85</v>
+      </c>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="19"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C21" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D21" s="45">
+        <v>2</v>
+      </c>
+      <c r="E21" s="45">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="G21" t="s" s="34">
+        <v>76</v>
+      </c>
+      <c r="H21" s="45">
+        <v>3</v>
+      </c>
+      <c r="I21" s="45">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="19"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C22" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D22" s="45">
+        <v>2</v>
+      </c>
+      <c r="E22" s="45">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s" s="34">
+        <v>87</v>
+      </c>
+      <c r="G22" t="s" s="34">
+        <v>78</v>
+      </c>
+      <c r="H22" s="45">
+        <v>2</v>
+      </c>
+      <c r="I22" s="45">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s" s="34">
+        <v>87</v>
+      </c>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="19"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C23" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D23" s="45">
+        <v>2</v>
+      </c>
+      <c r="E23" s="45">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s" s="34">
+        <v>88</v>
+      </c>
+      <c r="G23" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="H23" s="45">
+        <v>0</v>
+      </c>
+      <c r="I23" s="45">
+        <v>3</v>
+      </c>
+      <c r="J23" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C24" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D24" s="45">
+        <v>2</v>
+      </c>
+      <c r="E24" s="45">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s" s="34">
+        <v>89</v>
+      </c>
+      <c r="G24" t="s" s="34">
+        <v>55</v>
+      </c>
+      <c r="H24" s="45">
+        <v>2</v>
+      </c>
+      <c r="I24" s="45">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s" s="34">
+        <v>89</v>
+      </c>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="19"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C25" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D25" s="45">
+        <v>3</v>
+      </c>
+      <c r="E25" s="45">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s" s="34">
+        <v>72</v>
+      </c>
+      <c r="G25" t="s" s="34">
+        <v>83</v>
+      </c>
+      <c r="H25" s="45">
+        <v>3</v>
+      </c>
+      <c r="I25" s="45">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s" s="34">
+        <v>72</v>
+      </c>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="19"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C26" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D26" s="45">
+        <v>3</v>
+      </c>
+      <c r="E26" s="45">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s" s="34">
+        <v>73</v>
+      </c>
+      <c r="G26" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="H26" s="45">
+        <v>0</v>
+      </c>
+      <c r="I26" s="45">
+        <v>3</v>
+      </c>
+      <c r="J26" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="19"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C27" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D27" s="45">
+        <v>3</v>
+      </c>
+      <c r="E27" s="45">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s" s="34">
+        <v>42</v>
+      </c>
+      <c r="G27" t="s" s="34">
+        <v>84</v>
+      </c>
+      <c r="H27" s="45">
+        <v>3</v>
+      </c>
+      <c r="I27" s="45">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s" s="34">
+        <v>42</v>
+      </c>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="19"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C28" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D28" s="45">
+        <v>3</v>
+      </c>
+      <c r="E28" s="45">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="G28" t="s" s="34">
+        <v>85</v>
+      </c>
+      <c r="H28" s="45">
+        <v>3</v>
+      </c>
+      <c r="I28" s="45">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="19"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B29" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C29" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D29" s="45">
+        <v>3</v>
+      </c>
+      <c r="E29" s="45">
+        <v>5</v>
+      </c>
+      <c r="F29" t="s" s="34">
+        <v>77</v>
+      </c>
+      <c r="G29" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="H29" s="45">
+        <v>0</v>
+      </c>
+      <c r="I29" s="45">
+        <v>3</v>
+      </c>
+      <c r="J29" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="19"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C30" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D30" s="45">
+        <v>3</v>
+      </c>
+      <c r="E30" s="45">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s" s="34">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="34">
+        <v>87</v>
+      </c>
+      <c r="H30" s="45">
+        <v>3</v>
+      </c>
+      <c r="I30" s="45">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s" s="34">
+        <v>79</v>
+      </c>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="19"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C31" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D31" s="45">
+        <v>3</v>
+      </c>
+      <c r="E31" s="45">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s" s="34">
+        <v>81</v>
+      </c>
+      <c r="G31" t="s" s="34">
+        <v>88</v>
+      </c>
+      <c r="H31" s="45">
+        <v>0</v>
+      </c>
+      <c r="I31" s="45">
+        <v>3</v>
+      </c>
+      <c r="J31" t="s" s="34">
+        <v>88</v>
+      </c>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="19"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C32" s="44">
+        <v>46095</v>
+      </c>
+      <c r="D32" s="45">
+        <v>3</v>
+      </c>
+      <c r="E32" s="45">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="G32" t="s" s="34">
+        <v>89</v>
+      </c>
+      <c r="H32" s="45">
+        <v>2</v>
+      </c>
+      <c r="I32" s="45">
+        <v>1</v>
+      </c>
+      <c r="J32" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="19"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B33" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C33" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D33" s="45">
+        <v>1</v>
+      </c>
+      <c r="E33" s="45">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s" s="34">
+        <v>72</v>
+      </c>
+      <c r="G33" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="H33" s="45">
+        <v>0</v>
+      </c>
+      <c r="I33" s="45">
+        <v>3</v>
+      </c>
+      <c r="J33" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="19"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B34" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C34" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D34" s="45">
+        <v>1</v>
+      </c>
+      <c r="E34" s="45">
+        <v>2</v>
+      </c>
+      <c r="F34" t="s" s="34">
+        <v>42</v>
+      </c>
+      <c r="G34" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="H34" s="45">
+        <v>0</v>
+      </c>
+      <c r="I34" s="45">
+        <v>3</v>
+      </c>
+      <c r="J34" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="19"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B35" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C35" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D35" s="45">
+        <v>1</v>
+      </c>
+      <c r="E35" s="45">
+        <v>3</v>
+      </c>
+      <c r="F35" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="G35" t="s" s="34">
+        <v>79</v>
+      </c>
+      <c r="H35" s="45">
+        <v>3</v>
+      </c>
+      <c r="I35" s="45">
+        <v>0</v>
+      </c>
+      <c r="J35" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="19"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B36" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C36" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D36" s="45">
+        <v>1</v>
+      </c>
+      <c r="E36" s="45">
+        <v>4</v>
+      </c>
+      <c r="F36" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="H36" s="45">
+        <v>3</v>
+      </c>
+      <c r="I36" s="45">
+        <v>0</v>
+      </c>
+      <c r="J36" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="19"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B37" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C37" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D37" s="45">
+        <v>2</v>
+      </c>
+      <c r="E37" s="45">
+        <v>1</v>
+      </c>
+      <c r="F37" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="G37" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="H37" s="45">
+        <v>0</v>
+      </c>
+      <c r="I37" s="45">
+        <v>3</v>
+      </c>
+      <c r="J37" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="19"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B38" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C38" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D38" s="45">
+        <v>2</v>
+      </c>
+      <c r="E38" s="45">
+        <v>2</v>
+      </c>
+      <c r="F38" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="G38" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="H38" s="45">
+        <v>3</v>
+      </c>
+      <c r="I38" s="45">
+        <v>0</v>
+      </c>
+      <c r="J38" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="19"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B39" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C39" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D39" s="45">
+        <v>3</v>
+      </c>
+      <c r="E39" s="45">
+        <v>1</v>
+      </c>
+      <c r="F39" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="G39" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="H39" s="45">
+        <v>3</v>
+      </c>
+      <c r="I39" s="45">
+        <v>2</v>
+      </c>
+      <c r="J39" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="22"/>
+      <c r="O39" t="s" s="46">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C40" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" t="s" s="34">
+        <v>62</v>
+      </c>
+      <c r="L40" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="M40" s="35"/>
+      <c r="N40" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O40" s="36"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C41" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" t="s" s="34">
+        <v>64</v>
+      </c>
+      <c r="L41" t="s" s="34">
+        <v>86</v>
+      </c>
+      <c r="M41" s="35"/>
+      <c r="N41" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O41" s="36"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C42" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" t="s" s="34">
+        <v>65</v>
+      </c>
+      <c r="L42" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="M42" s="35"/>
+      <c r="N42" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O42" s="36"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C43" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" t="s" s="34">
+        <v>65</v>
+      </c>
+      <c r="L43" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="M43" s="18"/>
+      <c r="N43" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O43" s="19"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C44" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L44" t="s" s="34">
+        <v>91</v>
+      </c>
+      <c r="M44" t="s" s="34">
+        <v>80</v>
+      </c>
+      <c r="N44" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O44" s="19"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C45" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L45" t="s" s="34">
+        <v>92</v>
+      </c>
+      <c r="M45" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="N45" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O45" s="19"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s" s="34">
+        <v>69</v>
+      </c>
+      <c r="C46" s="44">
+        <v>46096</v>
+      </c>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L46" t="s" s="34">
+        <v>93</v>
+      </c>
+      <c r="M46" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="N46" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O46" s="19"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" t="s" s="37">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s" s="38">
+        <v>69</v>
+      </c>
+      <c r="C47" s="48">
+        <v>46096</v>
+      </c>
+      <c r="D47" s="39"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="39"/>
+      <c r="J47" s="39"/>
+      <c r="K47" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="L47" t="s" s="38">
+        <v>94</v>
+      </c>
+      <c r="M47" t="s" s="38">
+        <v>86</v>
+      </c>
+      <c r="N47" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O47" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="D3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O31"/>
+  <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.85" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="8.17188" style="49" customWidth="1"/>
+    <col min="2" max="2" width="63.1484" style="49" customWidth="1"/>
+    <col min="3" max="3" width="10.1719" style="49" customWidth="1"/>
+    <col min="4" max="5" width="4.85156" style="49" customWidth="1"/>
+    <col min="6" max="7" width="9.35156" style="49" customWidth="1"/>
+    <col min="8" max="9" width="8.17188" style="49" customWidth="1"/>
+    <col min="10" max="10" width="9.35156" style="49" customWidth="1"/>
+    <col min="11" max="11" width="8.17188" style="49" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="49" customWidth="1"/>
+    <col min="13" max="13" width="9.17188" style="49" customWidth="1"/>
+    <col min="14" max="14" width="8.17188" style="49" customWidth="1"/>
+    <col min="15" max="15" width="26.5" style="49" customWidth="1"/>
+    <col min="16" max="16384" width="8.35156" style="49" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.6" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" ht="21.7" customHeight="1">
+      <c r="A2" t="s" s="5">
+        <v>95</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" ht="13.1" customHeight="1">
+      <c r="A3" t="s" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s" s="9">
+        <v>95</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" t="s" s="9">
+        <v>3</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" ht="20.25" customHeight="1">
+      <c r="A4" t="s" s="12">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="50">
+        <v>96</v>
+      </c>
+      <c r="C4" t="s" s="51">
+        <v>97</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" t="s" s="16">
+        <v>6</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="19"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" t="s" s="16">
+        <v>7</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="19"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" t="s" s="20">
+        <v>8</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="23"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" t="s" s="29">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s" s="30">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s" s="30">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s" s="30">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s" s="30">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s" s="30">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s" s="30">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s" s="30">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s" s="30">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s" s="30">
+        <v>19</v>
+      </c>
+      <c r="L8" t="s" s="30">
+        <v>20</v>
+      </c>
+      <c r="M8" t="s" s="30">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s" s="30">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s" s="43">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C9" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D9" s="45">
+        <v>1</v>
+      </c>
+      <c r="E9" s="45">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="34">
+        <v>99</v>
+      </c>
+      <c r="H9" s="45">
+        <v>2</v>
+      </c>
+      <c r="I9" s="45">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="19"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C10" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D10" s="45">
+        <v>1</v>
+      </c>
+      <c r="E10" s="45">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s" s="34">
+        <v>87</v>
+      </c>
+      <c r="G10" t="s" s="34">
+        <v>83</v>
+      </c>
+      <c r="H10" s="45">
+        <v>2</v>
+      </c>
+      <c r="I10" s="45">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s" s="34">
+        <v>87</v>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="19"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D11" s="45">
+        <v>1</v>
+      </c>
+      <c r="E11" s="45">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s" s="34">
+        <v>52</v>
+      </c>
+      <c r="G11" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="H11" s="45">
+        <v>0</v>
+      </c>
+      <c r="I11" s="45">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="19"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C12" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D12" s="45">
+        <v>1</v>
+      </c>
+      <c r="E12" s="45">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s" s="34">
+        <v>100</v>
+      </c>
+      <c r="G12" t="s" s="34">
+        <v>101</v>
+      </c>
+      <c r="H12" s="45">
+        <v>0</v>
+      </c>
+      <c r="I12" s="45">
+        <v>3</v>
+      </c>
+      <c r="J12" t="s" s="34">
+        <v>101</v>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="19"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C13" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D13" s="45">
+        <v>2</v>
+      </c>
+      <c r="E13" s="45">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="G13" t="s" s="34">
+        <v>102</v>
+      </c>
+      <c r="H13" s="45">
+        <v>3</v>
+      </c>
+      <c r="I13" s="45">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="19"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C14" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D14" s="45">
+        <v>2</v>
+      </c>
+      <c r="E14" s="45">
+        <v>2</v>
+      </c>
+      <c r="F14" t="s" s="34">
+        <v>101</v>
+      </c>
+      <c r="G14" t="s" s="34">
+        <v>103</v>
+      </c>
+      <c r="H14" s="45">
+        <v>1</v>
+      </c>
+      <c r="I14" s="45">
+        <v>2</v>
+      </c>
+      <c r="J14" t="s" s="34">
+        <v>103</v>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="19"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C15" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D15" s="45">
+        <v>2</v>
+      </c>
+      <c r="E15" s="45">
+        <v>3</v>
+      </c>
+      <c r="F15" t="s" s="34">
+        <v>99</v>
+      </c>
+      <c r="G15" t="s" s="34">
+        <v>57</v>
+      </c>
+      <c r="H15" s="45">
+        <v>3</v>
+      </c>
+      <c r="I15" s="45">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s" s="34">
+        <v>99</v>
+      </c>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="19"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D16" s="45">
+        <v>2</v>
+      </c>
+      <c r="E16" s="45">
+        <v>4</v>
+      </c>
+      <c r="F16" t="s" s="34">
+        <v>83</v>
+      </c>
+      <c r="G16" t="s" s="34">
+        <v>33</v>
+      </c>
+      <c r="H16" s="45">
+        <v>2</v>
+      </c>
+      <c r="I16" s="45">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s" s="34">
+        <v>83</v>
+      </c>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D17" s="45">
+        <v>3</v>
+      </c>
+      <c r="E17" s="45">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s" s="34">
+        <v>33</v>
+      </c>
+      <c r="G17" t="s" s="34">
+        <v>87</v>
+      </c>
+      <c r="H17" s="45">
+        <v>2</v>
+      </c>
+      <c r="I17" s="45">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s" s="34">
+        <v>33</v>
+      </c>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="19"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C18" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D18" s="45">
+        <v>3</v>
+      </c>
+      <c r="E18" s="45">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s" s="34">
+        <v>57</v>
+      </c>
+      <c r="G18" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="H18" s="45">
+        <v>0</v>
+      </c>
+      <c r="I18" s="45">
+        <v>3</v>
+      </c>
+      <c r="J18" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="19"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C19" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D19" s="45">
+        <v>3</v>
+      </c>
+      <c r="E19" s="45">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s" s="34">
+        <v>103</v>
+      </c>
+      <c r="G19" t="s" s="34">
+        <v>100</v>
+      </c>
+      <c r="H19" s="45">
+        <v>3</v>
+      </c>
+      <c r="I19" s="45">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s" s="34">
+        <v>103</v>
+      </c>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="19"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C20" t="s" s="34">
+        <v>98</v>
+      </c>
+      <c r="D20" s="45">
+        <v>3</v>
+      </c>
+      <c r="E20" s="45">
+        <v>4</v>
+      </c>
+      <c r="F20" t="s" s="34">
+        <v>102</v>
+      </c>
+      <c r="G20" t="s" s="34">
+        <v>52</v>
+      </c>
+      <c r="H20" s="45">
+        <v>0</v>
+      </c>
+      <c r="I20" s="45">
+        <v>3</v>
+      </c>
+      <c r="J20" t="s" s="34">
+        <v>52</v>
+      </c>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="19"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D21" s="45">
+        <v>1</v>
+      </c>
+      <c r="E21" s="45">
+        <v>1</v>
+      </c>
+      <c r="F21" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s" s="34">
+        <v>33</v>
+      </c>
+      <c r="H21" s="45">
+        <v>3</v>
+      </c>
+      <c r="I21" s="45">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="19"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C22" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D22" s="45">
+        <v>1</v>
+      </c>
+      <c r="E22" s="45">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="G22" t="s" s="34">
+        <v>103</v>
+      </c>
+      <c r="H22" s="45">
+        <v>2</v>
+      </c>
+      <c r="I22" s="45">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="19"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C23" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D23" s="45">
+        <v>2</v>
+      </c>
+      <c r="E23" s="45">
+        <v>1</v>
+      </c>
+      <c r="F23" t="s" s="34">
+        <v>33</v>
+      </c>
+      <c r="G23" t="s" s="34">
+        <v>103</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" t="s" s="34">
+        <v>103</v>
+      </c>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" t="s" s="46">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C24" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D24" s="45">
+        <v>3</v>
+      </c>
+      <c r="E24" s="45">
+        <v>1</v>
+      </c>
+      <c r="F24" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="G24" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="22"/>
+      <c r="O24" t="s" s="46">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C25" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" t="s" s="34">
+        <v>62</v>
+      </c>
+      <c r="L25" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="M25" s="35"/>
+      <c r="N25" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O25" s="36"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C26" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" t="s" s="34">
+        <v>64</v>
+      </c>
+      <c r="L26" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="M26" s="35"/>
+      <c r="N26" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O26" s="36"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C27" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" t="s" s="34">
+        <v>65</v>
+      </c>
+      <c r="L27" t="s" s="34">
+        <v>103</v>
+      </c>
+      <c r="M27" s="35"/>
+      <c r="N27" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O27" s="36"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C28" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L28" t="s" s="34">
+        <v>105</v>
+      </c>
+      <c r="M28" t="s" s="34">
+        <v>45</v>
+      </c>
+      <c r="N28" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O28" s="19"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C29" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L29" t="s" s="34">
+        <v>106</v>
+      </c>
+      <c r="M29" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="N29" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O29" s="19"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s" s="34">
+        <v>95</v>
+      </c>
+      <c r="C30" t="s" s="34">
+        <v>104</v>
+      </c>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L30" t="s" s="34">
+        <v>107</v>
+      </c>
+      <c r="M30" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="N30" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O30" s="19"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" t="s" s="37">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s" s="38">
+        <v>95</v>
+      </c>
+      <c r="C31" t="s" s="38">
+        <v>104</v>
+      </c>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="L31" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="M31" t="s" s="38">
+        <v>103</v>
+      </c>
+      <c r="N31" t="s" s="40">
+        <v>68</v>
+      </c>
+      <c r="O31" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="D3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O36"/>
+  <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.85" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="8.17188" style="52" customWidth="1"/>
+    <col min="2" max="2" width="26.5" style="52" customWidth="1"/>
+    <col min="3" max="3" width="10.1719" style="52" customWidth="1"/>
+    <col min="4" max="5" width="4.85156" style="52" customWidth="1"/>
+    <col min="6" max="6" width="14.8516" style="52" customWidth="1"/>
+    <col min="7" max="7" width="20" style="52" customWidth="1"/>
+    <col min="8" max="9" width="8.17188" style="52" customWidth="1"/>
+    <col min="10" max="10" width="12.6719" style="52" customWidth="1"/>
+    <col min="11" max="11" width="11.1719" style="52" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="52" customWidth="1"/>
+    <col min="13" max="13" width="9.17188" style="52" customWidth="1"/>
+    <col min="14" max="14" width="8.17188" style="52" customWidth="1"/>
+    <col min="15" max="15" width="26.5" style="52" customWidth="1"/>
+    <col min="16" max="16384" width="8.35156" style="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.6" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" ht="21.7" customHeight="1">
+      <c r="A2" t="s" s="5">
+        <v>109</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="7"/>
+    </row>
+    <row r="3" ht="13.1" customHeight="1">
+      <c r="A3" t="s" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s" s="9">
+        <v>109</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" t="s" s="9">
+        <v>3</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="11"/>
+    </row>
+    <row r="4" ht="20.25" customHeight="1">
+      <c r="A4" t="s" s="12">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="13">
+        <v>110</v>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="O4" s="15"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" t="s" s="16">
+        <v>6</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="19"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" t="s" s="16">
+        <v>7</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="19"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" t="s" s="20">
+        <v>8</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="23"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" t="s" s="29">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s" s="30">
+        <v>10</v>
+      </c>
+      <c r="C8" t="s" s="30">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s" s="30">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s" s="30">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s" s="30">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s" s="30">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s" s="30">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s" s="30">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s" s="30">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s" s="30">
+        <v>19</v>
+      </c>
+      <c r="L8" t="s" s="30">
+        <v>20</v>
+      </c>
+      <c r="M8" t="s" s="30">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s" s="30">
+        <v>22</v>
+      </c>
+      <c r="O8" t="s" s="43">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C9" s="53">
+        <v>46004</v>
+      </c>
+      <c r="D9" s="45">
+        <v>1</v>
+      </c>
+      <c r="E9" s="45">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s" s="34">
+        <v>111</v>
+      </c>
+      <c r="G9" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="H9" s="45">
+        <v>0</v>
+      </c>
+      <c r="I9" s="45">
+        <v>3</v>
+      </c>
+      <c r="J9" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="19"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C10" s="54">
+        <v>46004</v>
+      </c>
+      <c r="D10" s="45">
+        <v>1</v>
+      </c>
+      <c r="E10" s="45">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s" s="34">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s" s="34">
+        <v>112</v>
+      </c>
+      <c r="H10" s="45">
+        <v>0</v>
+      </c>
+      <c r="I10" s="45">
+        <v>3</v>
+      </c>
+      <c r="J10" t="s" s="34">
+        <v>112</v>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="19"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C11" s="53">
+        <v>46004</v>
+      </c>
+      <c r="D11" s="45">
+        <v>1</v>
+      </c>
+      <c r="E11" s="45">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s" s="34">
+        <v>113</v>
+      </c>
+      <c r="G11" t="s" s="34">
+        <v>114</v>
+      </c>
+      <c r="H11" s="45">
+        <v>2</v>
+      </c>
+      <c r="I11" s="45">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s" s="34">
+        <v>113</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="19"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C12" s="54">
+        <v>46004</v>
+      </c>
+      <c r="D12" s="45">
+        <v>1</v>
+      </c>
+      <c r="E12" s="45">
+        <v>4</v>
+      </c>
+      <c r="F12" t="s" s="34">
+        <v>115</v>
+      </c>
+      <c r="G12" t="s" s="34">
+        <v>116</v>
+      </c>
+      <c r="H12" s="45">
+        <v>1</v>
+      </c>
+      <c r="I12" s="45">
+        <v>2</v>
+      </c>
+      <c r="J12" t="s" s="34">
+        <v>116</v>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="19"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C13" s="53">
+        <v>46004</v>
+      </c>
+      <c r="D13" s="45">
+        <v>1</v>
+      </c>
+      <c r="E13" s="45">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s" s="34">
+        <v>117</v>
+      </c>
+      <c r="G13" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="H13" s="45">
+        <v>0</v>
+      </c>
+      <c r="I13" s="45">
+        <v>3</v>
+      </c>
+      <c r="J13" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="19"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C14" s="54">
+        <v>46004</v>
+      </c>
+      <c r="D14" s="45">
+        <v>2</v>
+      </c>
+      <c r="E14" s="45">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="G14" t="s" s="34">
+        <v>111</v>
+      </c>
+      <c r="H14" s="45">
+        <v>3</v>
+      </c>
+      <c r="I14" s="45">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="19"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C15" s="53">
+        <v>46004</v>
+      </c>
+      <c r="D15" s="45">
+        <v>2</v>
+      </c>
+      <c r="E15" s="45">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="G15" t="s" s="34">
+        <v>118</v>
+      </c>
+      <c r="H15" s="45">
+        <v>3</v>
+      </c>
+      <c r="I15" s="45">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="19"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C16" s="54">
+        <v>46004</v>
+      </c>
+      <c r="D16" s="45">
+        <v>2</v>
+      </c>
+      <c r="E16" s="45">
+        <v>3</v>
+      </c>
+      <c r="F16" t="s" s="34">
+        <v>112</v>
+      </c>
+      <c r="G16" t="s" s="34">
+        <v>36</v>
+      </c>
+      <c r="H16" s="45">
+        <v>0</v>
+      </c>
+      <c r="I16" s="45">
+        <v>3</v>
+      </c>
+      <c r="J16" t="s" s="34">
+        <v>36</v>
+      </c>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C17" s="53">
+        <v>46004</v>
+      </c>
+      <c r="D17" s="45">
+        <v>2</v>
+      </c>
+      <c r="E17" s="45">
+        <v>4</v>
+      </c>
+      <c r="F17" t="s" s="34">
+        <v>119</v>
+      </c>
+      <c r="G17" t="s" s="34">
+        <v>120</v>
+      </c>
+      <c r="H17" s="45">
+        <v>0</v>
+      </c>
+      <c r="I17" s="45">
+        <v>3</v>
+      </c>
+      <c r="J17" t="s" s="34">
+        <v>120</v>
+      </c>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="19"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C18" s="54">
+        <v>46004</v>
+      </c>
+      <c r="D18" s="45">
+        <v>2</v>
+      </c>
+      <c r="E18" s="45">
+        <v>5</v>
+      </c>
+      <c r="F18" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="G18" t="s" s="34">
+        <v>117</v>
+      </c>
+      <c r="H18" s="45">
+        <v>3</v>
+      </c>
+      <c r="I18" s="45">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="19"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C19" s="53">
+        <v>46004</v>
+      </c>
+      <c r="D19" s="45">
+        <v>3</v>
+      </c>
+      <c r="E19" s="45">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s" s="34">
+        <v>114</v>
+      </c>
+      <c r="G19" t="s" s="34">
+        <v>113</v>
+      </c>
+      <c r="H19" s="45">
+        <v>0</v>
+      </c>
+      <c r="I19" s="45">
+        <v>3</v>
+      </c>
+      <c r="J19" t="s" s="34">
+        <v>113</v>
+      </c>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="19"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C20" s="54">
+        <v>46004</v>
+      </c>
+      <c r="D20" s="45">
+        <v>3</v>
+      </c>
+      <c r="E20" s="45">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s" s="34">
+        <v>118</v>
+      </c>
+      <c r="G20" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="H20" s="45">
+        <v>0</v>
+      </c>
+      <c r="I20" s="45">
+        <v>3</v>
+      </c>
+      <c r="J20" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="19"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C21" s="53">
+        <v>46004</v>
+      </c>
+      <c r="D21" s="45">
+        <v>3</v>
+      </c>
+      <c r="E21" s="45">
+        <v>3</v>
+      </c>
+      <c r="F21" t="s" s="34">
+        <v>120</v>
+      </c>
+      <c r="G21" t="s" s="34">
+        <v>119</v>
+      </c>
+      <c r="H21" s="45">
+        <v>1</v>
+      </c>
+      <c r="I21" s="45">
+        <v>2</v>
+      </c>
+      <c r="J21" t="s" s="34">
+        <v>119</v>
+      </c>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="19"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C22" s="54">
+        <v>46004</v>
+      </c>
+      <c r="D22" s="45">
+        <v>3</v>
+      </c>
+      <c r="E22" s="45">
+        <v>4</v>
+      </c>
+      <c r="F22" t="s" s="34">
+        <v>116</v>
+      </c>
+      <c r="G22" t="s" s="34">
+        <v>115</v>
+      </c>
+      <c r="H22" s="45">
+        <v>2</v>
+      </c>
+      <c r="I22" s="45">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s" s="34">
+        <v>116</v>
+      </c>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="19"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C23" s="53">
+        <v>46005</v>
+      </c>
+      <c r="D23" s="45">
+        <v>1</v>
+      </c>
+      <c r="E23" s="45">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s" s="34">
+        <v>120</v>
+      </c>
+      <c r="G23" t="s" s="34">
+        <v>113</v>
+      </c>
+      <c r="H23" s="45">
+        <v>0</v>
+      </c>
+      <c r="I23" s="45">
+        <v>3</v>
+      </c>
+      <c r="J23" t="s" s="34">
+        <v>113</v>
+      </c>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C24" s="53">
+        <v>46005</v>
+      </c>
+      <c r="D24" s="45">
+        <v>1</v>
+      </c>
+      <c r="E24" s="45">
+        <v>3</v>
+      </c>
+      <c r="F24" t="s" s="34">
+        <v>112</v>
+      </c>
+      <c r="G24" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="H24" s="45">
+        <v>0</v>
+      </c>
+      <c r="I24" s="45">
+        <v>3</v>
+      </c>
+      <c r="J24" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="19"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C25" s="53">
+        <v>46005</v>
+      </c>
+      <c r="D25" s="45">
+        <v>1</v>
+      </c>
+      <c r="E25" s="45">
+        <v>4</v>
+      </c>
+      <c r="F25" t="s" s="34">
+        <v>116</v>
+      </c>
+      <c r="G25" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="H25" s="45">
+        <v>1</v>
+      </c>
+      <c r="I25" s="45">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="19"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C26" s="53">
+        <v>46005</v>
+      </c>
+      <c r="D26" s="45">
+        <v>2</v>
+      </c>
+      <c r="E26" s="45">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s" s="34">
+        <v>113</v>
+      </c>
+      <c r="G26" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="H26" s="45">
+        <v>1</v>
+      </c>
+      <c r="I26" s="45">
+        <v>2</v>
+      </c>
+      <c r="J26" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="19"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B27" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C27" s="53">
+        <v>46005</v>
+      </c>
+      <c r="D27" s="45">
+        <v>2</v>
+      </c>
+      <c r="E27" s="45">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="G27" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="H27" s="45">
+        <v>0</v>
+      </c>
+      <c r="I27" s="45">
+        <v>3</v>
+      </c>
+      <c r="J27" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="19"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" t="s" s="33">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C28" s="53">
+        <v>46005</v>
+      </c>
+      <c r="D28" s="45">
+        <v>1</v>
+      </c>
+      <c r="E28" s="45">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="G28" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="19"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B29" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" t="s" s="34">
+        <v>62</v>
+      </c>
+      <c r="L29" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="M29" t="s" s="55">
+        <v>75</v>
+      </c>
+      <c r="N29" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O29" s="36"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B30" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" t="s" s="34">
+        <v>64</v>
+      </c>
+      <c r="L30" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="M30" t="s" s="55">
+        <v>82</v>
+      </c>
+      <c r="N30" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O30" s="36"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" t="s" s="34">
+        <v>65</v>
+      </c>
+      <c r="L31" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="M31" t="s" s="55">
+        <v>51</v>
+      </c>
+      <c r="N31" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O31" s="36"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" t="s" s="34">
+        <v>121</v>
+      </c>
+      <c r="L32" t="s" s="34">
+        <v>113</v>
+      </c>
+      <c r="M32" t="s" s="55">
+        <v>113</v>
+      </c>
+      <c r="N32" t="s" s="26">
+        <v>63</v>
+      </c>
+      <c r="O32" s="36"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B33" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L33" t="s" s="34">
+        <v>122</v>
+      </c>
+      <c r="M33" t="s" s="34">
+        <v>75</v>
+      </c>
+      <c r="N33" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O33" s="19"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L34" t="s" s="34">
+        <v>123</v>
+      </c>
+      <c r="M34" t="s" s="34">
+        <v>82</v>
+      </c>
+      <c r="N34" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O34" s="19"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" t="s" s="33">
+        <v>61</v>
+      </c>
+      <c r="B35" t="s" s="34">
+        <v>109</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" t="s" s="34">
+        <v>66</v>
+      </c>
+      <c r="L35" t="s" s="34">
+        <v>92</v>
+      </c>
+      <c r="M35" t="s" s="34">
+        <v>51</v>
+      </c>
+      <c r="N35" t="s" s="47">
+        <v>68</v>
+      </c>
+      <c r="O35" s="19"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" t="s" s="37">
+        <v>61</v>
+      </c>
+      <c r="B36" t="s" s="38">
+        <v>109</v>
+      </c>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+      <c r="K36" t="s" s="38">
+        <v>66</v>
+      </c>
+      <c r="L36" t="s" s="38">
+        <v>124</v>
+      </c>
+      <c r="M36" t="s" s="38">
+        <v>113</v>
+      </c>
+      <c r="N36" t="s" s="40">
+        <v>68</v>
+      </c>
+      <c r="O36" s="41"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="D3:O3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="19.85" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="8.17188" style="56" customWidth="1"/>
+    <col min="2" max="2" width="26.5" style="56" customWidth="1"/>
+    <col min="3" max="3" width="10.1719" style="56" customWidth="1"/>
+    <col min="4" max="5" width="4.85156" style="56" customWidth="1"/>
+    <col min="6" max="7" width="9.35156" style="56" customWidth="1"/>
+    <col min="8" max="9" width="8.17188" style="56" customWidth="1"/>
+    <col min="10" max="10" width="9.35156" style="56" customWidth="1"/>
+    <col min="11" max="11" width="8.17188" style="56" customWidth="1"/>
+    <col min="12" max="12" width="6.5" style="56" customWidth="1"/>
+    <col min="13" max="13" width="9.17188" style="56" customWidth="1"/>
+    <col min="14" max="14" width="8.17188" style="56" customWidth="1"/>
+    <col min="15" max="15" width="26.5" style="56" customWidth="1"/>
+    <col min="16" max="16384" width="8.35156" style="56" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="1" ht="21.7" customHeight="1">
       <c r="A1" t="s" s="5">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -4112,7 +8161,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s" s="9">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" t="s" s="9">
@@ -4135,7 +8184,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s" s="13">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
@@ -4209,852 +8258,852 @@
       <c r="O6" s="23"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" t="s" s="43">
+      <c r="A7" t="s" s="57">
         <v>9</v>
       </c>
-      <c r="B7" t="s" s="44">
+      <c r="B7" t="s" s="58">
         <v>10</v>
       </c>
-      <c r="C7" t="s" s="44">
+      <c r="C7" t="s" s="58">
         <v>11</v>
       </c>
-      <c r="D7" t="s" s="44">
+      <c r="D7" t="s" s="58">
         <v>12</v>
       </c>
-      <c r="E7" t="s" s="44">
+      <c r="E7" t="s" s="58">
         <v>13</v>
       </c>
-      <c r="F7" t="s" s="44">
+      <c r="F7" t="s" s="58">
         <v>14</v>
       </c>
-      <c r="G7" t="s" s="44">
+      <c r="G7" t="s" s="58">
         <v>15</v>
       </c>
-      <c r="H7" t="s" s="44">
+      <c r="H7" t="s" s="58">
         <v>16</v>
       </c>
-      <c r="I7" t="s" s="44">
+      <c r="I7" t="s" s="58">
         <v>17</v>
       </c>
-      <c r="J7" t="s" s="44">
+      <c r="J7" t="s" s="58">
         <v>18</v>
       </c>
-      <c r="K7" t="s" s="44">
+      <c r="K7" t="s" s="58">
         <v>19</v>
       </c>
-      <c r="L7" t="s" s="44">
+      <c r="L7" t="s" s="58">
         <v>20</v>
       </c>
-      <c r="M7" t="s" s="44">
+      <c r="M7" t="s" s="58">
         <v>21</v>
       </c>
-      <c r="N7" t="s" s="44">
+      <c r="N7" t="s" s="58">
         <v>22</v>
       </c>
-      <c r="O7" t="s" s="45">
+      <c r="O7" t="s" s="59">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B8" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D8" s="48">
-        <v>1</v>
-      </c>
-      <c r="E8" s="48">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s" s="47">
-        <v>72</v>
-      </c>
-      <c r="G8" t="s" s="47">
-        <v>73</v>
-      </c>
-      <c r="H8" s="48">
-        <v>3</v>
-      </c>
-      <c r="I8" s="48">
+      <c r="A8" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C8" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D8" s="62">
+        <v>1</v>
+      </c>
+      <c r="E8" s="62">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s" s="61">
+        <v>82</v>
+      </c>
+      <c r="G8" t="s" s="61">
+        <v>128</v>
+      </c>
+      <c r="H8" s="62">
+        <v>3</v>
+      </c>
+      <c r="I8" s="62">
         <v>0</v>
       </c>
-      <c r="J8" t="s" s="47">
-        <v>72</v>
-      </c>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="50"/>
+      <c r="J8" t="s" s="61">
+        <v>82</v>
+      </c>
+      <c r="K8" s="63"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="64"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D9" s="48">
-        <v>1</v>
-      </c>
-      <c r="E9" s="48">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s" s="47">
-        <v>74</v>
-      </c>
-      <c r="G9" t="s" s="47">
-        <v>75</v>
-      </c>
-      <c r="H9" s="48">
-        <v>2</v>
-      </c>
-      <c r="I9" s="48">
-        <v>1</v>
-      </c>
-      <c r="J9" t="s" s="47">
-        <v>74</v>
-      </c>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="50"/>
+      <c r="A9" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C9" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D9" s="62">
+        <v>1</v>
+      </c>
+      <c r="E9" s="62">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s" s="61">
+        <v>129</v>
+      </c>
+      <c r="G9" t="s" s="61">
+        <v>130</v>
+      </c>
+      <c r="H9" s="62">
+        <v>2</v>
+      </c>
+      <c r="I9" s="62">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s" s="61">
+        <v>129</v>
+      </c>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="64"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D10" s="48">
-        <v>1</v>
-      </c>
-      <c r="E10" s="48">
-        <v>3</v>
-      </c>
-      <c r="F10" t="s" s="47">
+      <c r="A10" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C10" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D10" s="62">
+        <v>1</v>
+      </c>
+      <c r="E10" s="62">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s" s="61">
+        <v>131</v>
+      </c>
+      <c r="G10" t="s" s="61">
+        <v>132</v>
+      </c>
+      <c r="H10" s="62">
+        <v>1</v>
+      </c>
+      <c r="I10" s="62">
+        <v>2</v>
+      </c>
+      <c r="J10" t="s" s="61">
+        <v>132</v>
+      </c>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="64"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C11" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D11" s="62">
+        <v>1</v>
+      </c>
+      <c r="E11" s="62">
+        <v>4</v>
+      </c>
+      <c r="F11" t="s" s="61">
+        <v>133</v>
+      </c>
+      <c r="G11" t="s" s="61">
+        <v>134</v>
+      </c>
+      <c r="H11" s="62">
+        <v>0</v>
+      </c>
+      <c r="I11" s="62">
+        <v>3</v>
+      </c>
+      <c r="J11" t="s" s="61">
+        <v>134</v>
+      </c>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="64"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B12" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C12" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D12" s="62">
+        <v>2</v>
+      </c>
+      <c r="E12" s="62">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s" s="61">
+        <v>130</v>
+      </c>
+      <c r="G12" t="s" s="61">
+        <v>135</v>
+      </c>
+      <c r="H12" s="62">
+        <v>3</v>
+      </c>
+      <c r="I12" s="62">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s" s="61">
+        <v>130</v>
+      </c>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" t="s" s="65">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C13" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D13" s="62">
+        <v>2</v>
+      </c>
+      <c r="E13" s="62">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s" s="61">
+        <v>134</v>
+      </c>
+      <c r="G13" t="s" s="61">
+        <v>133</v>
+      </c>
+      <c r="H13" s="62">
+        <v>3</v>
+      </c>
+      <c r="I13" s="62">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s" s="61">
+        <v>134</v>
+      </c>
+      <c r="K13" s="63"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="64"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C14" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D14" s="62">
+        <v>2</v>
+      </c>
+      <c r="E14" s="62">
+        <v>3</v>
+      </c>
+      <c r="F14" t="s" s="61">
         <v>76</v>
       </c>
-      <c r="G10" t="s" s="47">
-        <v>77</v>
-      </c>
-      <c r="H10" s="48">
-        <v>1</v>
-      </c>
-      <c r="I10" s="48">
-        <v>2</v>
-      </c>
-      <c r="J10" t="s" s="47">
-        <v>77</v>
-      </c>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
-      <c r="N10" s="49"/>
-      <c r="O10" s="50"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D11" s="48">
-        <v>1</v>
-      </c>
-      <c r="E11" s="48">
+      <c r="G14" t="s" s="61">
+        <v>137</v>
+      </c>
+      <c r="H14" s="62">
+        <v>3</v>
+      </c>
+      <c r="I14" s="62">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s" s="61">
+        <v>76</v>
+      </c>
+      <c r="K14" s="63"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" t="s" s="65">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C15" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D15" s="62">
+        <v>2</v>
+      </c>
+      <c r="E15" s="62">
         <v>4</v>
       </c>
-      <c r="F11" t="s" s="47">
-        <v>78</v>
-      </c>
-      <c r="G11" t="s" s="47">
-        <v>79</v>
-      </c>
-      <c r="H11" s="48">
+      <c r="F15" t="s" s="61">
+        <v>132</v>
+      </c>
+      <c r="G15" t="s" s="61">
+        <v>131</v>
+      </c>
+      <c r="H15" s="62">
         <v>0</v>
       </c>
-      <c r="I11" s="48">
-        <v>3</v>
-      </c>
-      <c r="J11" t="s" s="47">
-        <v>79</v>
-      </c>
-      <c r="K11" s="49"/>
-      <c r="L11" s="49"/>
-      <c r="M11" s="49"/>
-      <c r="N11" s="49"/>
-      <c r="O11" s="50"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B12" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D12" s="48">
-        <v>2</v>
-      </c>
-      <c r="E12" s="48">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s" s="47">
-        <v>75</v>
-      </c>
-      <c r="G12" t="s" s="47">
-        <v>80</v>
-      </c>
-      <c r="H12" s="48">
-        <v>3</v>
-      </c>
-      <c r="I12" s="48">
+      <c r="I15" s="62">
+        <v>3</v>
+      </c>
+      <c r="J15" t="s" s="61">
+        <v>131</v>
+      </c>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="64"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C16" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D16" s="62">
+        <v>3</v>
+      </c>
+      <c r="E16" s="62">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s" s="61">
+        <v>135</v>
+      </c>
+      <c r="G16" t="s" s="61">
+        <v>129</v>
+      </c>
+      <c r="H16" s="62">
         <v>0</v>
       </c>
-      <c r="J12" t="s" s="47">
-        <v>75</v>
-      </c>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" t="s" s="51">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D13" s="48">
-        <v>2</v>
-      </c>
-      <c r="E13" s="48">
-        <v>2</v>
-      </c>
-      <c r="F13" t="s" s="47">
-        <v>79</v>
-      </c>
-      <c r="G13" t="s" s="47">
-        <v>78</v>
-      </c>
-      <c r="H13" s="48">
-        <v>3</v>
-      </c>
-      <c r="I13" s="48">
+      <c r="I16" s="62">
+        <v>3</v>
+      </c>
+      <c r="J16" t="s" s="61">
+        <v>129</v>
+      </c>
+      <c r="K16" s="63"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="63"/>
+      <c r="N16" s="63"/>
+      <c r="O16" t="s" s="65">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C17" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D17" s="62">
+        <v>3</v>
+      </c>
+      <c r="E17" s="62">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s" s="61">
+        <v>137</v>
+      </c>
+      <c r="G17" t="s" s="61">
+        <v>76</v>
+      </c>
+      <c r="H17" s="62">
         <v>0</v>
       </c>
-      <c r="J13" t="s" s="47">
-        <v>79</v>
-      </c>
-      <c r="K13" s="49"/>
-      <c r="L13" s="49"/>
-      <c r="M13" s="49"/>
-      <c r="N13" s="49"/>
-      <c r="O13" s="50"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D14" s="48">
-        <v>2</v>
-      </c>
-      <c r="E14" s="48">
-        <v>3</v>
-      </c>
-      <c r="F14" t="s" s="47">
+      <c r="I17" s="62">
+        <v>3</v>
+      </c>
+      <c r="J17" t="s" s="61">
+        <v>76</v>
+      </c>
+      <c r="K17" s="63"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="63"/>
+      <c r="N17" s="63"/>
+      <c r="O17" t="s" s="65">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B18" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C18" t="s" s="61">
+        <v>127</v>
+      </c>
+      <c r="D18" s="62">
+        <v>3</v>
+      </c>
+      <c r="E18" s="62">
+        <v>3</v>
+      </c>
+      <c r="F18" t="s" s="61">
+        <v>141</v>
+      </c>
+      <c r="G18" t="s" s="61">
         <v>82</v>
       </c>
-      <c r="G14" t="s" s="47">
-        <v>83</v>
-      </c>
-      <c r="H14" s="48">
-        <v>3</v>
-      </c>
-      <c r="I14" s="48">
+      <c r="H18" s="62">
         <v>0</v>
       </c>
-      <c r="J14" t="s" s="47">
+      <c r="I18" s="62">
+        <v>3</v>
+      </c>
+      <c r="J18" t="s" s="61">
         <v>82</v>
       </c>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
-      <c r="N14" s="49"/>
-      <c r="O14" t="s" s="51">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D15" s="48">
-        <v>2</v>
-      </c>
-      <c r="E15" s="48">
-        <v>4</v>
-      </c>
-      <c r="F15" t="s" s="47">
-        <v>77</v>
-      </c>
-      <c r="G15" t="s" s="47">
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="64"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C19" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D19" s="62">
+        <v>1</v>
+      </c>
+      <c r="E19" s="62">
+        <v>1</v>
+      </c>
+      <c r="F19" t="s" s="61">
+        <v>131</v>
+      </c>
+      <c r="G19" t="s" s="61">
+        <v>134</v>
+      </c>
+      <c r="H19" s="62">
+        <v>1</v>
+      </c>
+      <c r="I19" s="62">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s" s="61">
+        <v>134</v>
+      </c>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="64"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C20" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D20" s="62">
+        <v>2</v>
+      </c>
+      <c r="E20" s="62">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s" s="61">
+        <v>134</v>
+      </c>
+      <c r="G20" t="s" s="61">
         <v>76</v>
       </c>
-      <c r="H15" s="48">
+      <c r="H20" s="62">
+        <v>1</v>
+      </c>
+      <c r="I20" s="62">
+        <v>2</v>
+      </c>
+      <c r="J20" t="s" s="61">
+        <v>76</v>
+      </c>
+      <c r="K20" s="63"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="64"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C21" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D21" s="62">
+        <v>2</v>
+      </c>
+      <c r="E21" s="62">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s" s="61">
+        <v>82</v>
+      </c>
+      <c r="G21" t="s" s="61">
+        <v>130</v>
+      </c>
+      <c r="H21" s="62">
+        <v>3</v>
+      </c>
+      <c r="I21" s="62">
         <v>0</v>
       </c>
-      <c r="I15" s="48">
-        <v>3</v>
-      </c>
-      <c r="J15" t="s" s="47">
+      <c r="J21" t="s" s="61">
+        <v>82</v>
+      </c>
+      <c r="K21" s="63"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="64"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" t="s" s="60">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C22" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D22" s="62">
+        <v>3</v>
+      </c>
+      <c r="E22" s="62">
+        <v>1</v>
+      </c>
+      <c r="F22" t="s" s="61">
+        <v>82</v>
+      </c>
+      <c r="G22" t="s" s="61">
         <v>76</v>
       </c>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="50"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C16" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D16" s="48">
-        <v>3</v>
-      </c>
-      <c r="E16" s="48">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s" s="47">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s" s="47">
-        <v>74</v>
-      </c>
-      <c r="H16" s="48">
-        <v>0</v>
-      </c>
-      <c r="I16" s="48">
-        <v>3</v>
-      </c>
-      <c r="J16" t="s" s="47">
-        <v>74</v>
-      </c>
-      <c r="K16" s="49"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="49"/>
-      <c r="N16" s="49"/>
-      <c r="O16" t="s" s="51">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D17" s="48">
-        <v>3</v>
-      </c>
-      <c r="E17" s="48">
-        <v>2</v>
-      </c>
-      <c r="F17" t="s" s="47">
-        <v>83</v>
-      </c>
-      <c r="G17" t="s" s="47">
-        <v>82</v>
-      </c>
-      <c r="H17" s="48">
-        <v>0</v>
-      </c>
-      <c r="I17" s="48">
-        <v>3</v>
-      </c>
-      <c r="J17" t="s" s="47">
-        <v>82</v>
-      </c>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" t="s" s="51">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B18" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C18" t="s" s="47">
-        <v>71</v>
-      </c>
-      <c r="D18" s="48">
-        <v>3</v>
-      </c>
-      <c r="E18" s="48">
-        <v>3</v>
-      </c>
-      <c r="F18" t="s" s="47">
-        <v>87</v>
-      </c>
-      <c r="G18" t="s" s="47">
-        <v>72</v>
-      </c>
-      <c r="H18" s="48">
-        <v>0</v>
-      </c>
-      <c r="I18" s="48">
-        <v>3</v>
-      </c>
-      <c r="J18" t="s" s="47">
-        <v>72</v>
-      </c>
-      <c r="K18" s="49"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="49"/>
-      <c r="N18" s="49"/>
-      <c r="O18" s="50"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B19" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C19" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D19" s="48">
-        <v>1</v>
-      </c>
-      <c r="E19" s="48">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s" s="47">
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" t="s" s="61">
         <v>76</v>
       </c>
-      <c r="G19" t="s" s="47">
-        <v>79</v>
-      </c>
-      <c r="H19" s="48">
-        <v>1</v>
-      </c>
-      <c r="I19" s="48">
-        <v>2</v>
-      </c>
-      <c r="J19" t="s" s="47">
-        <v>79</v>
-      </c>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="50"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B20" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C20" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D20" s="48">
-        <v>2</v>
-      </c>
-      <c r="E20" s="48">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s" s="47">
-        <v>79</v>
-      </c>
-      <c r="G20" t="s" s="47">
-        <v>82</v>
-      </c>
-      <c r="H20" s="48">
-        <v>1</v>
-      </c>
-      <c r="I20" s="48">
-        <v>2</v>
-      </c>
-      <c r="J20" t="s" s="47">
-        <v>82</v>
-      </c>
-      <c r="K20" s="49"/>
-      <c r="L20" s="49"/>
-      <c r="M20" s="49"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="50"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B21" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D21" s="48">
-        <v>2</v>
-      </c>
-      <c r="E21" s="48">
-        <v>2</v>
-      </c>
-      <c r="F21" t="s" s="47">
-        <v>72</v>
-      </c>
-      <c r="G21" t="s" s="47">
-        <v>75</v>
-      </c>
-      <c r="H21" s="48">
-        <v>3</v>
-      </c>
-      <c r="I21" s="48">
-        <v>0</v>
-      </c>
-      <c r="J21" t="s" s="47">
-        <v>72</v>
-      </c>
-      <c r="K21" s="49"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="50"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" t="s" s="46">
-        <v>24</v>
-      </c>
-      <c r="B22" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C22" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D22" s="48">
-        <v>3</v>
-      </c>
-      <c r="E22" s="48">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s" s="47">
-        <v>72</v>
-      </c>
-      <c r="G22" t="s" s="47">
-        <v>82</v>
-      </c>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" t="s" s="47">
-        <v>82</v>
-      </c>
-      <c r="K22" s="49"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="52"/>
-      <c r="O22" t="s" s="51">
-        <v>89</v>
+      <c r="K22" s="63"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="66"/>
+      <c r="O22" t="s" s="65">
+        <v>143</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" t="s" s="46">
+      <c r="A23" t="s" s="60">
         <v>61</v>
       </c>
-      <c r="B23" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C23" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" t="s" s="47">
+      <c r="B23" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C23" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
+      <c r="K23" t="s" s="61">
         <v>62</v>
       </c>
-      <c r="L23" t="s" s="47">
-        <v>82</v>
-      </c>
-      <c r="M23" s="53"/>
+      <c r="L23" t="s" s="61">
+        <v>76</v>
+      </c>
+      <c r="M23" s="67"/>
       <c r="N23" t="s" s="26">
         <v>63</v>
       </c>
-      <c r="O23" s="54"/>
+      <c r="O23" s="68"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" t="s" s="46">
+      <c r="A24" t="s" s="60">
         <v>61</v>
       </c>
-      <c r="B24" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C24" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" t="s" s="47">
+      <c r="B24" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C24" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63"/>
+      <c r="J24" s="63"/>
+      <c r="K24" t="s" s="61">
         <v>64</v>
       </c>
-      <c r="L24" t="s" s="47">
-        <v>72</v>
-      </c>
-      <c r="M24" s="53"/>
+      <c r="L24" t="s" s="61">
+        <v>82</v>
+      </c>
+      <c r="M24" s="67"/>
       <c r="N24" t="s" s="26">
         <v>63</v>
       </c>
-      <c r="O24" s="54"/>
+      <c r="O24" s="68"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" t="s" s="46">
+      <c r="A25" t="s" s="60">
         <v>61</v>
       </c>
-      <c r="B25" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" t="s" s="47">
+      <c r="B25" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C25" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
+      <c r="F25" s="63"/>
+      <c r="G25" s="63"/>
+      <c r="H25" s="63"/>
+      <c r="I25" s="63"/>
+      <c r="J25" s="63"/>
+      <c r="K25" t="s" s="61">
         <v>65</v>
       </c>
-      <c r="L25" t="s" s="47">
-        <v>79</v>
-      </c>
-      <c r="M25" s="53"/>
+      <c r="L25" t="s" s="61">
+        <v>134</v>
+      </c>
+      <c r="M25" s="67"/>
       <c r="N25" t="s" s="26">
         <v>63</v>
       </c>
-      <c r="O25" s="54"/>
+      <c r="O25" s="68"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" t="s" s="46">
+      <c r="A26" t="s" s="60">
         <v>61</v>
       </c>
-      <c r="B26" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C26" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" t="s" s="47">
-        <v>90</v>
-      </c>
-      <c r="L26" t="s" s="47">
-        <v>75</v>
-      </c>
-      <c r="M26" s="53"/>
+      <c r="B26" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C26" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" t="s" s="61">
+        <v>121</v>
+      </c>
+      <c r="L26" t="s" s="61">
+        <v>130</v>
+      </c>
+      <c r="M26" s="67"/>
       <c r="N26" t="s" s="26">
         <v>63</v>
       </c>
-      <c r="O26" s="54"/>
+      <c r="O26" s="68"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" t="s" s="46">
+      <c r="A27" t="s" s="60">
         <v>61</v>
       </c>
-      <c r="B27" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C27" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" t="s" s="47">
+      <c r="B27" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C27" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D27" s="63"/>
+      <c r="E27" s="63"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+      <c r="I27" s="63"/>
+      <c r="J27" s="63"/>
+      <c r="K27" t="s" s="61">
         <v>66</v>
       </c>
-      <c r="L27" t="s" s="47">
-        <v>91</v>
-      </c>
-      <c r="M27" t="s" s="47">
-        <v>82</v>
+      <c r="L27" t="s" s="61">
+        <v>144</v>
+      </c>
+      <c r="M27" t="s" s="61">
+        <v>76</v>
       </c>
       <c r="N27" t="s" s="30">
         <v>68</v>
       </c>
-      <c r="O27" s="50"/>
+      <c r="O27" s="64"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" t="s" s="46">
+      <c r="A28" t="s" s="60">
         <v>61</v>
       </c>
-      <c r="B28" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C28" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" t="s" s="47">
-        <v>92</v>
-      </c>
-      <c r="L28" t="s" s="47">
-        <v>93</v>
-      </c>
-      <c r="M28" t="s" s="47">
-        <v>72</v>
+      <c r="B28" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C28" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D28" s="63"/>
+      <c r="E28" s="63"/>
+      <c r="F28" s="63"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="63"/>
+      <c r="K28" t="s" s="61">
+        <v>145</v>
+      </c>
+      <c r="L28" t="s" s="61">
+        <v>146</v>
+      </c>
+      <c r="M28" t="s" s="61">
+        <v>82</v>
       </c>
       <c r="N28" t="s" s="34">
         <v>68</v>
       </c>
-      <c r="O28" s="50"/>
+      <c r="O28" s="64"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" t="s" s="46">
+      <c r="A29" t="s" s="60">
         <v>61</v>
       </c>
-      <c r="B29" t="s" s="47">
-        <v>69</v>
-      </c>
-      <c r="C29" t="s" s="47">
-        <v>88</v>
-      </c>
-      <c r="D29" s="49"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" t="s" s="47">
-        <v>92</v>
-      </c>
-      <c r="L29" t="s" s="47">
-        <v>94</v>
-      </c>
-      <c r="M29" t="s" s="47">
-        <v>79</v>
+      <c r="B29" t="s" s="61">
+        <v>125</v>
+      </c>
+      <c r="C29" t="s" s="61">
+        <v>142</v>
+      </c>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
+      <c r="F29" s="63"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
+      <c r="K29" t="s" s="61">
+        <v>145</v>
+      </c>
+      <c r="L29" t="s" s="61">
+        <v>147</v>
+      </c>
+      <c r="M29" t="s" s="61">
+        <v>134</v>
       </c>
       <c r="N29" t="s" s="34">
         <v>68</v>
       </c>
-      <c r="O29" s="50"/>
+      <c r="O29" s="64"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" t="s" s="55">
+      <c r="A30" t="s" s="69">
         <v>61</v>
       </c>
-      <c r="B30" t="s" s="56">
-        <v>69</v>
-      </c>
-      <c r="C30" t="s" s="56">
-        <v>88</v>
-      </c>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" t="s" s="56">
-        <v>92</v>
-      </c>
-      <c r="L30" t="s" s="56">
-        <v>95</v>
-      </c>
-      <c r="M30" t="s" s="56">
-        <v>75</v>
+      <c r="B30" t="s" s="70">
+        <v>125</v>
+      </c>
+      <c r="C30" t="s" s="70">
+        <v>142</v>
+      </c>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" t="s" s="70">
+        <v>145</v>
+      </c>
+      <c r="L30" t="s" s="70">
+        <v>148</v>
+      </c>
+      <c r="M30" t="s" s="70">
+        <v>130</v>
       </c>
       <c r="N30" t="s" s="38">
         <v>68</v>
       </c>
-      <c r="O30" s="58"/>
+      <c r="O30" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="2">
